--- a/samples/ss_gucl_ingest.xlsx
+++ b/samples/ss_gucl_ingest.xlsx
@@ -495,7 +495,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R42"/>
+  <dimension ref="A1:U42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -536,57 +536,72 @@
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>Bus 150 kV</t>
+          <t>Bus HV</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
+          <t>Bus LV</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
           <t>Jumlah Trafo</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>Jumlah Kapasitor</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>Catatan Simbol</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>Jumlah Sirkit Bay</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>Status Operasi</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>Role</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>Status Kerawanan</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>No Kerawanan</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>Wilayah</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>Sudut Pandang</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>Latitude</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>Longitude</t>
         </is>
       </c>
     </row>
@@ -623,24 +638,25 @@
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>Beroperasi</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr"/>
-      <c r="O2" t="inlineStr">
+      <c r="M2" t="inlineStr"/>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>Beroperasi</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr"/>
+      <c r="P2" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="P2" t="inlineStr"/>
-      <c r="Q2" t="inlineStr">
-        <is>
-          <t>Banten</t>
-        </is>
-      </c>
-      <c r="R2" t="inlineStr"/>
+      <c r="Q2" t="inlineStr"/>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>Banten</t>
+        </is>
+      </c>
+      <c r="S2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -671,46 +687,47 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
+          <t>1,2,3</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr"/>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>CLBRU</t>
+        </is>
+      </c>
+      <c r="J3" t="n">
+        <v>3</v>
+      </c>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>3 IBT (unit 1,2,3)</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr"/>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>Beroperasi</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Rawan</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>CLBRU</t>
-        </is>
-      </c>
-      <c r="I3" t="n">
-        <v>3</v>
-      </c>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>3 IBT (unit 1,2,3)</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>Beroperasi</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr"/>
-      <c r="O3" t="inlineStr">
-        <is>
-          <t>Rawan</t>
-        </is>
-      </c>
-      <c r="P3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="Q3" t="inlineStr">
-        <is>
-          <t>Banten</t>
-        </is>
-      </c>
-      <c r="R3" t="inlineStr"/>
+      <c r="R3" t="inlineStr">
+        <is>
+          <t>Banten</t>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -745,24 +762,25 @@
       <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>Beroperasi</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr"/>
-      <c r="O4" t="inlineStr">
+      <c r="M4" t="inlineStr"/>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>Beroperasi</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="P4" t="inlineStr"/>
-      <c r="Q4" t="inlineStr">
-        <is>
-          <t>Banten</t>
-        </is>
-      </c>
-      <c r="R4" t="inlineStr"/>
+      <c r="Q4" t="inlineStr"/>
+      <c r="R4" t="inlineStr">
+        <is>
+          <t>Banten</t>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -797,24 +815,25 @@
       <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>Beroperasi</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr"/>
-      <c r="O5" t="inlineStr">
+      <c r="M5" t="inlineStr"/>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>Beroperasi</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="P5" t="inlineStr"/>
-      <c r="Q5" t="inlineStr">
-        <is>
-          <t>Banten</t>
-        </is>
-      </c>
-      <c r="R5" t="inlineStr"/>
+      <c r="Q5" t="inlineStr"/>
+      <c r="R5" t="inlineStr">
+        <is>
+          <t>Banten</t>
+        </is>
+      </c>
+      <c r="S5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -849,24 +868,25 @@
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>Beroperasi</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr"/>
-      <c r="O6" t="inlineStr">
+      <c r="M6" t="inlineStr"/>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>Beroperasi</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="P6" t="inlineStr"/>
-      <c r="Q6" t="inlineStr">
-        <is>
-          <t>Banten</t>
-        </is>
-      </c>
-      <c r="R6" t="inlineStr"/>
+      <c r="Q6" t="inlineStr"/>
+      <c r="R6" t="inlineStr">
+        <is>
+          <t>Banten</t>
+        </is>
+      </c>
+      <c r="S6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -901,28 +921,29 @@
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>Beroperasi</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr"/>
-      <c r="O7" t="inlineStr">
+      <c r="M7" t="inlineStr"/>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>Beroperasi</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
         <is>
           <t>Rawan</t>
         </is>
       </c>
-      <c r="P7" t="inlineStr">
+      <c r="Q7" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="Q7" t="inlineStr">
-        <is>
-          <t>Banten</t>
-        </is>
-      </c>
-      <c r="R7" t="inlineStr"/>
+      <c r="R7" t="inlineStr">
+        <is>
+          <t>Banten</t>
+        </is>
+      </c>
+      <c r="S7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -957,24 +978,25 @@
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>Beroperasi</t>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr"/>
-      <c r="O8" t="inlineStr">
+      <c r="M8" t="inlineStr"/>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>Beroperasi</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="P8" t="inlineStr"/>
-      <c r="Q8" t="inlineStr">
-        <is>
-          <t>Banten</t>
-        </is>
-      </c>
-      <c r="R8" t="inlineStr"/>
+      <c r="Q8" t="inlineStr"/>
+      <c r="R8" t="inlineStr">
+        <is>
+          <t>Banten</t>
+        </is>
+      </c>
+      <c r="S8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1009,28 +1031,29 @@
       <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>Beroperasi</t>
-        </is>
-      </c>
-      <c r="N9" t="inlineStr"/>
-      <c r="O9" t="inlineStr">
+      <c r="M9" t="inlineStr"/>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>Beroperasi</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
         <is>
           <t>Rawan</t>
         </is>
       </c>
-      <c r="P9" t="inlineStr">
+      <c r="Q9" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="Q9" t="inlineStr">
-        <is>
-          <t>Banten</t>
-        </is>
-      </c>
-      <c r="R9" t="inlineStr"/>
+      <c r="R9" t="inlineStr">
+        <is>
+          <t>Banten</t>
+        </is>
+      </c>
+      <c r="S9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1065,28 +1088,29 @@
       <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>Beroperasi</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr"/>
-      <c r="O10" t="inlineStr">
+      <c r="M10" t="inlineStr"/>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>Beroperasi</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
         <is>
           <t>Rawan</t>
         </is>
       </c>
-      <c r="P10" t="inlineStr">
+      <c r="Q10" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="Q10" t="inlineStr">
-        <is>
-          <t>Banten</t>
-        </is>
-      </c>
-      <c r="R10" t="inlineStr"/>
+      <c r="R10" t="inlineStr">
+        <is>
+          <t>Banten</t>
+        </is>
+      </c>
+      <c r="S10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1121,24 +1145,25 @@
       <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>Beroperasi</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr"/>
-      <c r="O11" t="inlineStr">
+      <c r="M11" t="inlineStr"/>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>Beroperasi</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="P11" t="inlineStr"/>
-      <c r="Q11" t="inlineStr">
-        <is>
-          <t>Banten</t>
-        </is>
-      </c>
-      <c r="R11" t="inlineStr"/>
+      <c r="Q11" t="inlineStr"/>
+      <c r="R11" t="inlineStr">
+        <is>
+          <t>Banten</t>
+        </is>
+      </c>
+      <c r="S11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1173,24 +1198,25 @@
       <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>Beroperasi</t>
-        </is>
-      </c>
-      <c r="N12" t="inlineStr"/>
-      <c r="O12" t="inlineStr">
+      <c r="M12" t="inlineStr"/>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>Beroperasi</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="P12" t="inlineStr"/>
-      <c r="Q12" t="inlineStr">
-        <is>
-          <t>Banten</t>
-        </is>
-      </c>
-      <c r="R12" t="inlineStr"/>
+      <c r="Q12" t="inlineStr"/>
+      <c r="R12" t="inlineStr">
+        <is>
+          <t>Banten</t>
+        </is>
+      </c>
+      <c r="S12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1225,28 +1251,29 @@
       <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr"/>
       <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>Beroperasi</t>
-        </is>
-      </c>
-      <c r="N13" t="inlineStr"/>
-      <c r="O13" t="inlineStr">
+      <c r="M13" t="inlineStr"/>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>Beroperasi</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
         <is>
           <t>Rawan</t>
         </is>
       </c>
-      <c r="P13" t="inlineStr">
+      <c r="Q13" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="Q13" t="inlineStr">
-        <is>
-          <t>Banten</t>
-        </is>
-      </c>
-      <c r="R13" t="inlineStr"/>
+      <c r="R13" t="inlineStr">
+        <is>
+          <t>Banten</t>
+        </is>
+      </c>
+      <c r="S13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1281,24 +1308,25 @@
       <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr"/>
       <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>Beroperasi</t>
-        </is>
-      </c>
-      <c r="N14" t="inlineStr"/>
-      <c r="O14" t="inlineStr">
+      <c r="M14" t="inlineStr"/>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>Beroperasi</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="P14" t="inlineStr"/>
-      <c r="Q14" t="inlineStr">
-        <is>
-          <t>Banten</t>
-        </is>
-      </c>
-      <c r="R14" t="inlineStr"/>
+      <c r="Q14" t="inlineStr"/>
+      <c r="R14" t="inlineStr">
+        <is>
+          <t>Banten</t>
+        </is>
+      </c>
+      <c r="S14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -1333,24 +1361,25 @@
       <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr"/>
       <c r="L15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>Beroperasi</t>
-        </is>
-      </c>
-      <c r="N15" t="inlineStr"/>
-      <c r="O15" t="inlineStr">
+      <c r="M15" t="inlineStr"/>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>Beroperasi</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="P15" t="inlineStr"/>
-      <c r="Q15" t="inlineStr">
-        <is>
-          <t>Banten</t>
-        </is>
-      </c>
-      <c r="R15" t="inlineStr"/>
+      <c r="Q15" t="inlineStr"/>
+      <c r="R15" t="inlineStr">
+        <is>
+          <t>Banten</t>
+        </is>
+      </c>
+      <c r="S15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -1385,24 +1414,25 @@
       <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr"/>
       <c r="L16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>Beroperasi</t>
-        </is>
-      </c>
-      <c r="N16" t="inlineStr"/>
-      <c r="O16" t="inlineStr">
+      <c r="M16" t="inlineStr"/>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>Beroperasi</t>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="P16" t="inlineStr"/>
-      <c r="Q16" t="inlineStr">
-        <is>
-          <t>Banten</t>
-        </is>
-      </c>
-      <c r="R16" t="inlineStr"/>
+      <c r="Q16" t="inlineStr"/>
+      <c r="R16" t="inlineStr">
+        <is>
+          <t>Banten</t>
+        </is>
+      </c>
+      <c r="S16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -1437,24 +1467,25 @@
       <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr"/>
       <c r="L17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>Beroperasi</t>
-        </is>
-      </c>
-      <c r="N17" t="inlineStr"/>
-      <c r="O17" t="inlineStr">
+      <c r="M17" t="inlineStr"/>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>Beroperasi</t>
+        </is>
+      </c>
+      <c r="O17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="P17" t="inlineStr"/>
-      <c r="Q17" t="inlineStr">
-        <is>
-          <t>Banten</t>
-        </is>
-      </c>
-      <c r="R17" t="inlineStr"/>
+      <c r="Q17" t="inlineStr"/>
+      <c r="R17" t="inlineStr">
+        <is>
+          <t>Banten</t>
+        </is>
+      </c>
+      <c r="S17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -1489,28 +1520,29 @@
       <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr"/>
       <c r="L18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>Beroperasi</t>
-        </is>
-      </c>
-      <c r="N18" t="inlineStr"/>
-      <c r="O18" t="inlineStr">
+      <c r="M18" t="inlineStr"/>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>Beroperasi</t>
+        </is>
+      </c>
+      <c r="O18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
         <is>
           <t>Rawan</t>
         </is>
       </c>
-      <c r="P18" t="inlineStr">
+      <c r="Q18" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="Q18" t="inlineStr">
-        <is>
-          <t>Banten</t>
-        </is>
-      </c>
-      <c r="R18" t="inlineStr"/>
+      <c r="R18" t="inlineStr">
+        <is>
+          <t>Banten</t>
+        </is>
+      </c>
+      <c r="S18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -1545,28 +1577,29 @@
       <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr"/>
       <c r="L19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>Beroperasi</t>
-        </is>
-      </c>
-      <c r="N19" t="inlineStr"/>
-      <c r="O19" t="inlineStr">
+      <c r="M19" t="inlineStr"/>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>Beroperasi</t>
+        </is>
+      </c>
+      <c r="O19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
         <is>
           <t>Rawan</t>
         </is>
       </c>
-      <c r="P19" t="inlineStr">
+      <c r="Q19" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="Q19" t="inlineStr">
-        <is>
-          <t>Banten</t>
-        </is>
-      </c>
-      <c r="R19" t="inlineStr"/>
+      <c r="R19" t="inlineStr">
+        <is>
+          <t>Banten</t>
+        </is>
+      </c>
+      <c r="S19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -1601,24 +1634,25 @@
       <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr"/>
       <c r="L20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>Beroperasi</t>
-        </is>
-      </c>
-      <c r="N20" t="inlineStr"/>
-      <c r="O20" t="inlineStr">
+      <c r="M20" t="inlineStr"/>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>Beroperasi</t>
+        </is>
+      </c>
+      <c r="O20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="P20" t="inlineStr"/>
-      <c r="Q20" t="inlineStr">
-        <is>
-          <t>Banten</t>
-        </is>
-      </c>
-      <c r="R20" t="inlineStr"/>
+      <c r="Q20" t="inlineStr"/>
+      <c r="R20" t="inlineStr">
+        <is>
+          <t>Banten</t>
+        </is>
+      </c>
+      <c r="S20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -1653,24 +1687,25 @@
       <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr"/>
       <c r="L21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>Beroperasi</t>
-        </is>
-      </c>
-      <c r="N21" t="inlineStr"/>
-      <c r="O21" t="inlineStr">
+      <c r="M21" t="inlineStr"/>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>Beroperasi</t>
+        </is>
+      </c>
+      <c r="O21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="P21" t="inlineStr"/>
-      <c r="Q21" t="inlineStr">
-        <is>
-          <t>Banten</t>
-        </is>
-      </c>
-      <c r="R21" t="inlineStr"/>
+      <c r="Q21" t="inlineStr"/>
+      <c r="R21" t="inlineStr">
+        <is>
+          <t>Banten</t>
+        </is>
+      </c>
+      <c r="S21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -1705,24 +1740,25 @@
       <c r="J22" t="inlineStr"/>
       <c r="K22" t="inlineStr"/>
       <c r="L22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>Beroperasi</t>
-        </is>
-      </c>
-      <c r="N22" t="inlineStr"/>
-      <c r="O22" t="inlineStr">
+      <c r="M22" t="inlineStr"/>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>Beroperasi</t>
+        </is>
+      </c>
+      <c r="O22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="P22" t="inlineStr"/>
-      <c r="Q22" t="inlineStr">
-        <is>
-          <t>Banten</t>
-        </is>
-      </c>
-      <c r="R22" t="inlineStr"/>
+      <c r="Q22" t="inlineStr"/>
+      <c r="R22" t="inlineStr">
+        <is>
+          <t>Banten</t>
+        </is>
+      </c>
+      <c r="S22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -1757,24 +1793,25 @@
       <c r="J23" t="inlineStr"/>
       <c r="K23" t="inlineStr"/>
       <c r="L23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>Beroperasi</t>
-        </is>
-      </c>
-      <c r="N23" t="inlineStr"/>
-      <c r="O23" t="inlineStr">
+      <c r="M23" t="inlineStr"/>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>Beroperasi</t>
+        </is>
+      </c>
+      <c r="O23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="P23" t="inlineStr"/>
-      <c r="Q23" t="inlineStr">
-        <is>
-          <t>Banten</t>
-        </is>
-      </c>
-      <c r="R23" t="inlineStr"/>
+      <c r="Q23" t="inlineStr"/>
+      <c r="R23" t="inlineStr">
+        <is>
+          <t>Banten</t>
+        </is>
+      </c>
+      <c r="S23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -1809,24 +1846,25 @@
       <c r="J24" t="inlineStr"/>
       <c r="K24" t="inlineStr"/>
       <c r="L24" t="inlineStr"/>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>Beroperasi</t>
-        </is>
-      </c>
-      <c r="N24" t="inlineStr"/>
-      <c r="O24" t="inlineStr">
+      <c r="M24" t="inlineStr"/>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>Beroperasi</t>
+        </is>
+      </c>
+      <c r="O24" t="inlineStr"/>
+      <c r="P24" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="P24" t="inlineStr"/>
-      <c r="Q24" t="inlineStr">
-        <is>
-          <t>Banten</t>
-        </is>
-      </c>
-      <c r="R24" t="inlineStr"/>
+      <c r="Q24" t="inlineStr"/>
+      <c r="R24" t="inlineStr">
+        <is>
+          <t>Banten</t>
+        </is>
+      </c>
+      <c r="S24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -1861,24 +1899,25 @@
       <c r="J25" t="inlineStr"/>
       <c r="K25" t="inlineStr"/>
       <c r="L25" t="inlineStr"/>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>Beroperasi</t>
-        </is>
-      </c>
-      <c r="N25" t="inlineStr"/>
-      <c r="O25" t="inlineStr">
+      <c r="M25" t="inlineStr"/>
+      <c r="N25" t="inlineStr">
+        <is>
+          <t>Beroperasi</t>
+        </is>
+      </c>
+      <c r="O25" t="inlineStr"/>
+      <c r="P25" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="P25" t="inlineStr"/>
-      <c r="Q25" t="inlineStr">
-        <is>
-          <t>Banten</t>
-        </is>
-      </c>
-      <c r="R25" t="inlineStr"/>
+      <c r="Q25" t="inlineStr"/>
+      <c r="R25" t="inlineStr">
+        <is>
+          <t>Banten</t>
+        </is>
+      </c>
+      <c r="S25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -1913,24 +1952,25 @@
       <c r="J26" t="inlineStr"/>
       <c r="K26" t="inlineStr"/>
       <c r="L26" t="inlineStr"/>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>Beroperasi</t>
-        </is>
-      </c>
-      <c r="N26" t="inlineStr"/>
-      <c r="O26" t="inlineStr">
+      <c r="M26" t="inlineStr"/>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>Beroperasi</t>
+        </is>
+      </c>
+      <c r="O26" t="inlineStr"/>
+      <c r="P26" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="P26" t="inlineStr"/>
-      <c r="Q26" t="inlineStr">
-        <is>
-          <t>Banten</t>
-        </is>
-      </c>
-      <c r="R26" t="inlineStr"/>
+      <c r="Q26" t="inlineStr"/>
+      <c r="R26" t="inlineStr">
+        <is>
+          <t>Banten</t>
+        </is>
+      </c>
+      <c r="S26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -1965,28 +2005,29 @@
       <c r="J27" t="inlineStr"/>
       <c r="K27" t="inlineStr"/>
       <c r="L27" t="inlineStr"/>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>Beroperasi</t>
-        </is>
-      </c>
-      <c r="N27" t="inlineStr"/>
-      <c r="O27" t="inlineStr">
+      <c r="M27" t="inlineStr"/>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>Beroperasi</t>
+        </is>
+      </c>
+      <c r="O27" t="inlineStr"/>
+      <c r="P27" t="inlineStr">
         <is>
           <t>Rawan</t>
         </is>
       </c>
-      <c r="P27" t="inlineStr">
+      <c r="Q27" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="Q27" t="inlineStr">
-        <is>
-          <t>Banten</t>
-        </is>
-      </c>
-      <c r="R27" t="inlineStr"/>
+      <c r="R27" t="inlineStr">
+        <is>
+          <t>Banten</t>
+        </is>
+      </c>
+      <c r="S27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -2021,24 +2062,25 @@
       <c r="J28" t="inlineStr"/>
       <c r="K28" t="inlineStr"/>
       <c r="L28" t="inlineStr"/>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>Beroperasi</t>
-        </is>
-      </c>
-      <c r="N28" t="inlineStr"/>
-      <c r="O28" t="inlineStr">
+      <c r="M28" t="inlineStr"/>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>Beroperasi</t>
+        </is>
+      </c>
+      <c r="O28" t="inlineStr"/>
+      <c r="P28" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="P28" t="inlineStr"/>
-      <c r="Q28" t="inlineStr">
-        <is>
-          <t>Banten</t>
-        </is>
-      </c>
-      <c r="R28" t="inlineStr"/>
+      <c r="Q28" t="inlineStr"/>
+      <c r="R28" t="inlineStr">
+        <is>
+          <t>Banten</t>
+        </is>
+      </c>
+      <c r="S28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -2073,28 +2115,29 @@
       <c r="J29" t="inlineStr"/>
       <c r="K29" t="inlineStr"/>
       <c r="L29" t="inlineStr"/>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>Beroperasi</t>
-        </is>
-      </c>
-      <c r="N29" t="inlineStr"/>
-      <c r="O29" t="inlineStr">
+      <c r="M29" t="inlineStr"/>
+      <c r="N29" t="inlineStr">
+        <is>
+          <t>Beroperasi</t>
+        </is>
+      </c>
+      <c r="O29" t="inlineStr"/>
+      <c r="P29" t="inlineStr">
         <is>
           <t>Rawan</t>
         </is>
       </c>
-      <c r="P29" t="inlineStr">
+      <c r="Q29" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="Q29" t="inlineStr">
-        <is>
-          <t>Banten</t>
-        </is>
-      </c>
-      <c r="R29" t="inlineStr"/>
+      <c r="R29" t="inlineStr">
+        <is>
+          <t>Banten</t>
+        </is>
+      </c>
+      <c r="S29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -2129,24 +2172,25 @@
       <c r="J30" t="inlineStr"/>
       <c r="K30" t="inlineStr"/>
       <c r="L30" t="inlineStr"/>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>Beroperasi</t>
-        </is>
-      </c>
-      <c r="N30" t="inlineStr"/>
-      <c r="O30" t="inlineStr">
+      <c r="M30" t="inlineStr"/>
+      <c r="N30" t="inlineStr">
+        <is>
+          <t>Beroperasi</t>
+        </is>
+      </c>
+      <c r="O30" t="inlineStr"/>
+      <c r="P30" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="P30" t="inlineStr"/>
-      <c r="Q30" t="inlineStr">
-        <is>
-          <t>Banten</t>
-        </is>
-      </c>
-      <c r="R30" t="inlineStr"/>
+      <c r="Q30" t="inlineStr"/>
+      <c r="R30" t="inlineStr">
+        <is>
+          <t>Banten</t>
+        </is>
+      </c>
+      <c r="S30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -2181,24 +2225,25 @@
       <c r="J31" t="inlineStr"/>
       <c r="K31" t="inlineStr"/>
       <c r="L31" t="inlineStr"/>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>Beroperasi</t>
-        </is>
-      </c>
-      <c r="N31" t="inlineStr"/>
-      <c r="O31" t="inlineStr">
+      <c r="M31" t="inlineStr"/>
+      <c r="N31" t="inlineStr">
+        <is>
+          <t>Beroperasi</t>
+        </is>
+      </c>
+      <c r="O31" t="inlineStr"/>
+      <c r="P31" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="P31" t="inlineStr"/>
-      <c r="Q31" t="inlineStr">
-        <is>
-          <t>Banten</t>
-        </is>
-      </c>
-      <c r="R31" t="inlineStr"/>
+      <c r="Q31" t="inlineStr"/>
+      <c r="R31" t="inlineStr">
+        <is>
+          <t>Banten</t>
+        </is>
+      </c>
+      <c r="S31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -2233,28 +2278,29 @@
       <c r="J32" t="inlineStr"/>
       <c r="K32" t="inlineStr"/>
       <c r="L32" t="inlineStr"/>
-      <c r="M32" t="inlineStr">
-        <is>
-          <t>Beroperasi</t>
-        </is>
-      </c>
-      <c r="N32" t="inlineStr"/>
-      <c r="O32" t="inlineStr">
+      <c r="M32" t="inlineStr"/>
+      <c r="N32" t="inlineStr">
+        <is>
+          <t>Beroperasi</t>
+        </is>
+      </c>
+      <c r="O32" t="inlineStr"/>
+      <c r="P32" t="inlineStr">
         <is>
           <t>Rawan</t>
         </is>
       </c>
-      <c r="P32" t="inlineStr">
+      <c r="Q32" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="Q32" t="inlineStr">
-        <is>
-          <t>Banten</t>
-        </is>
-      </c>
-      <c r="R32" t="inlineStr"/>
+      <c r="R32" t="inlineStr">
+        <is>
+          <t>Banten</t>
+        </is>
+      </c>
+      <c r="S32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -2289,28 +2335,29 @@
       <c r="J33" t="inlineStr"/>
       <c r="K33" t="inlineStr"/>
       <c r="L33" t="inlineStr"/>
-      <c r="M33" t="inlineStr">
-        <is>
-          <t>Beroperasi</t>
-        </is>
-      </c>
-      <c r="N33" t="inlineStr"/>
-      <c r="O33" t="inlineStr">
+      <c r="M33" t="inlineStr"/>
+      <c r="N33" t="inlineStr">
+        <is>
+          <t>Beroperasi</t>
+        </is>
+      </c>
+      <c r="O33" t="inlineStr"/>
+      <c r="P33" t="inlineStr">
         <is>
           <t>Rawan</t>
         </is>
       </c>
-      <c r="P33" t="inlineStr">
+      <c r="Q33" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="Q33" t="inlineStr">
-        <is>
-          <t>Banten</t>
-        </is>
-      </c>
-      <c r="R33" t="inlineStr"/>
+      <c r="R33" t="inlineStr">
+        <is>
+          <t>Banten</t>
+        </is>
+      </c>
+      <c r="S33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -2345,24 +2392,25 @@
       <c r="J34" t="inlineStr"/>
       <c r="K34" t="inlineStr"/>
       <c r="L34" t="inlineStr"/>
-      <c r="M34" t="inlineStr">
-        <is>
-          <t>Beroperasi</t>
-        </is>
-      </c>
-      <c r="N34" t="inlineStr"/>
-      <c r="O34" t="inlineStr">
+      <c r="M34" t="inlineStr"/>
+      <c r="N34" t="inlineStr">
+        <is>
+          <t>Beroperasi</t>
+        </is>
+      </c>
+      <c r="O34" t="inlineStr"/>
+      <c r="P34" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="P34" t="inlineStr"/>
-      <c r="Q34" t="inlineStr">
-        <is>
-          <t>Banten</t>
-        </is>
-      </c>
-      <c r="R34" t="inlineStr"/>
+      <c r="Q34" t="inlineStr"/>
+      <c r="R34" t="inlineStr">
+        <is>
+          <t>Banten</t>
+        </is>
+      </c>
+      <c r="S34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -2397,24 +2445,25 @@
       <c r="J35" t="inlineStr"/>
       <c r="K35" t="inlineStr"/>
       <c r="L35" t="inlineStr"/>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>Beroperasi</t>
-        </is>
-      </c>
-      <c r="N35" t="inlineStr"/>
-      <c r="O35" t="inlineStr">
+      <c r="M35" t="inlineStr"/>
+      <c r="N35" t="inlineStr">
+        <is>
+          <t>Beroperasi</t>
+        </is>
+      </c>
+      <c r="O35" t="inlineStr"/>
+      <c r="P35" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="P35" t="inlineStr"/>
-      <c r="Q35" t="inlineStr">
-        <is>
-          <t>Banten</t>
-        </is>
-      </c>
-      <c r="R35" t="inlineStr"/>
+      <c r="Q35" t="inlineStr"/>
+      <c r="R35" t="inlineStr">
+        <is>
+          <t>Banten</t>
+        </is>
+      </c>
+      <c r="S35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -2449,24 +2498,25 @@
       <c r="J36" t="inlineStr"/>
       <c r="K36" t="inlineStr"/>
       <c r="L36" t="inlineStr"/>
-      <c r="M36" t="inlineStr">
-        <is>
-          <t>Beroperasi</t>
-        </is>
-      </c>
-      <c r="N36" t="inlineStr"/>
-      <c r="O36" t="inlineStr">
+      <c r="M36" t="inlineStr"/>
+      <c r="N36" t="inlineStr">
+        <is>
+          <t>Beroperasi</t>
+        </is>
+      </c>
+      <c r="O36" t="inlineStr"/>
+      <c r="P36" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="P36" t="inlineStr"/>
-      <c r="Q36" t="inlineStr">
-        <is>
-          <t>Banten</t>
-        </is>
-      </c>
-      <c r="R36" t="inlineStr"/>
+      <c r="Q36" t="inlineStr"/>
+      <c r="R36" t="inlineStr">
+        <is>
+          <t>Banten</t>
+        </is>
+      </c>
+      <c r="S36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -2501,28 +2551,29 @@
       <c r="J37" t="inlineStr"/>
       <c r="K37" t="inlineStr"/>
       <c r="L37" t="inlineStr"/>
-      <c r="M37" t="inlineStr">
-        <is>
-          <t>Beroperasi</t>
-        </is>
-      </c>
-      <c r="N37" t="inlineStr"/>
-      <c r="O37" t="inlineStr">
+      <c r="M37" t="inlineStr"/>
+      <c r="N37" t="inlineStr">
+        <is>
+          <t>Beroperasi</t>
+        </is>
+      </c>
+      <c r="O37" t="inlineStr"/>
+      <c r="P37" t="inlineStr">
         <is>
           <t>Rawan</t>
         </is>
       </c>
-      <c r="P37" t="inlineStr">
+      <c r="Q37" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="Q37" t="inlineStr">
-        <is>
-          <t>Banten</t>
-        </is>
-      </c>
-      <c r="R37" t="inlineStr"/>
+      <c r="R37" t="inlineStr">
+        <is>
+          <t>Banten</t>
+        </is>
+      </c>
+      <c r="S37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -2557,28 +2608,29 @@
       <c r="J38" t="inlineStr"/>
       <c r="K38" t="inlineStr"/>
       <c r="L38" t="inlineStr"/>
-      <c r="M38" t="inlineStr">
-        <is>
-          <t>Beroperasi</t>
-        </is>
-      </c>
-      <c r="N38" t="inlineStr"/>
-      <c r="O38" t="inlineStr">
+      <c r="M38" t="inlineStr"/>
+      <c r="N38" t="inlineStr">
+        <is>
+          <t>Beroperasi</t>
+        </is>
+      </c>
+      <c r="O38" t="inlineStr"/>
+      <c r="P38" t="inlineStr">
         <is>
           <t>Rawan</t>
         </is>
       </c>
-      <c r="P38" t="inlineStr">
+      <c r="Q38" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="Q38" t="inlineStr">
-        <is>
-          <t>Banten</t>
-        </is>
-      </c>
-      <c r="R38" t="inlineStr"/>
+      <c r="R38" t="inlineStr">
+        <is>
+          <t>Banten</t>
+        </is>
+      </c>
+      <c r="S38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -2613,24 +2665,25 @@
       <c r="J39" t="inlineStr"/>
       <c r="K39" t="inlineStr"/>
       <c r="L39" t="inlineStr"/>
-      <c r="M39" t="inlineStr">
-        <is>
-          <t>Beroperasi</t>
-        </is>
-      </c>
-      <c r="N39" t="inlineStr"/>
-      <c r="O39" t="inlineStr">
+      <c r="M39" t="inlineStr"/>
+      <c r="N39" t="inlineStr">
+        <is>
+          <t>Beroperasi</t>
+        </is>
+      </c>
+      <c r="O39" t="inlineStr"/>
+      <c r="P39" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="P39" t="inlineStr"/>
-      <c r="Q39" t="inlineStr">
-        <is>
-          <t>Banten</t>
-        </is>
-      </c>
-      <c r="R39" t="inlineStr"/>
+      <c r="Q39" t="inlineStr"/>
+      <c r="R39" t="inlineStr">
+        <is>
+          <t>Banten</t>
+        </is>
+      </c>
+      <c r="S39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -2665,28 +2718,29 @@
       <c r="J40" t="inlineStr"/>
       <c r="K40" t="inlineStr"/>
       <c r="L40" t="inlineStr"/>
-      <c r="M40" t="inlineStr">
-        <is>
-          <t>Beroperasi</t>
-        </is>
-      </c>
-      <c r="N40" t="inlineStr"/>
-      <c r="O40" t="inlineStr">
+      <c r="M40" t="inlineStr"/>
+      <c r="N40" t="inlineStr">
+        <is>
+          <t>Beroperasi</t>
+        </is>
+      </c>
+      <c r="O40" t="inlineStr"/>
+      <c r="P40" t="inlineStr">
         <is>
           <t>Rawan</t>
         </is>
       </c>
-      <c r="P40" t="inlineStr">
+      <c r="Q40" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="Q40" t="inlineStr">
-        <is>
-          <t>Banten</t>
-        </is>
-      </c>
-      <c r="R40" t="inlineStr"/>
+      <c r="R40" t="inlineStr">
+        <is>
+          <t>Banten</t>
+        </is>
+      </c>
+      <c r="S40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -2721,24 +2775,25 @@
       <c r="J41" t="inlineStr"/>
       <c r="K41" t="inlineStr"/>
       <c r="L41" t="inlineStr"/>
-      <c r="M41" t="inlineStr">
-        <is>
-          <t>Beroperasi</t>
-        </is>
-      </c>
-      <c r="N41" t="inlineStr"/>
-      <c r="O41" t="inlineStr">
+      <c r="M41" t="inlineStr"/>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>Beroperasi</t>
+        </is>
+      </c>
+      <c r="O41" t="inlineStr"/>
+      <c r="P41" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="P41" t="inlineStr"/>
-      <c r="Q41" t="inlineStr">
-        <is>
-          <t>Banten</t>
-        </is>
-      </c>
-      <c r="R41" t="inlineStr"/>
+      <c r="Q41" t="inlineStr"/>
+      <c r="R41" t="inlineStr">
+        <is>
+          <t>Banten</t>
+        </is>
+      </c>
+      <c r="S41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -2773,24 +2828,25 @@
       <c r="J42" t="inlineStr"/>
       <c r="K42" t="inlineStr"/>
       <c r="L42" t="inlineStr"/>
-      <c r="M42" t="inlineStr">
-        <is>
-          <t>Beroperasi</t>
-        </is>
-      </c>
-      <c r="N42" t="inlineStr"/>
-      <c r="O42" t="inlineStr">
+      <c r="M42" t="inlineStr"/>
+      <c r="N42" t="inlineStr">
+        <is>
+          <t>Beroperasi</t>
+        </is>
+      </c>
+      <c r="O42" t="inlineStr"/>
+      <c r="P42" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="P42" t="inlineStr"/>
-      <c r="Q42" t="inlineStr">
-        <is>
-          <t>Banten</t>
-        </is>
-      </c>
-      <c r="R42" t="inlineStr"/>
+      <c r="Q42" t="inlineStr"/>
+      <c r="R42" t="inlineStr">
+        <is>
+          <t>Banten</t>
+        </is>
+      </c>
+      <c r="S42" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/samples/ss_gucl_ingest.xlsx
+++ b/samples/ss_gucl_ingest.xlsx
@@ -5730,7 +5730,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I20"/>
+  <dimension ref="A1:J20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5756,25 +5756,30 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
+          <t>Jenis</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
           <t>Tegangan</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Jumlah Sirkit</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Status Operasi</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>No Kerawanan</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>Sudut Pandang</t>
         </is>
@@ -5799,21 +5804,22 @@
           <t>CLBRU</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>150 kV</t>
-        </is>
-      </c>
-      <c r="F2" t="n">
+      <c r="E2" t="inlineStr"/>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>150 kV</t>
+        </is>
+      </c>
+      <c r="G2" t="n">
         <v>1</v>
       </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>Beroperasi</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr"/>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>Beroperasi</t>
+        </is>
+      </c>
       <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -5834,21 +5840,22 @@
           <t>MNA</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>150 kV</t>
-        </is>
-      </c>
-      <c r="F3" t="n">
+      <c r="E3" t="inlineStr"/>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>150 kV</t>
+        </is>
+      </c>
+      <c r="G3" t="n">
         <v>1</v>
       </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>Beroperasi</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr"/>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>Beroperasi</t>
+        </is>
+      </c>
       <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -5869,21 +5876,22 @@
           <t>ALNDO</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>150 kV</t>
-        </is>
-      </c>
-      <c r="F4" t="n">
+      <c r="E4" t="inlineStr"/>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>150 kV</t>
+        </is>
+      </c>
+      <c r="G4" t="n">
         <v>1</v>
       </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>Beroperasi</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr"/>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Beroperasi</t>
+        </is>
+      </c>
       <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -5904,21 +5912,22 @@
           <t>INFRO</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>150 kV</t>
-        </is>
-      </c>
-      <c r="F5" t="n">
+      <c r="E5" t="inlineStr"/>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>150 kV</t>
+        </is>
+      </c>
+      <c r="G5" t="n">
         <v>1</v>
       </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>Beroperasi</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr"/>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Beroperasi</t>
+        </is>
+      </c>
       <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -5939,21 +5948,22 @@
           <t>INFRO</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>150 kV</t>
-        </is>
-      </c>
-      <c r="F6" t="n">
+      <c r="E6" t="inlineStr"/>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>150 kV</t>
+        </is>
+      </c>
+      <c r="G6" t="n">
         <v>1</v>
       </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>Beroperasi</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr"/>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Beroperasi</t>
+        </is>
+      </c>
       <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -5974,21 +5984,22 @@
           <t>POLMA</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>150 kV</t>
-        </is>
-      </c>
-      <c r="F7" t="n">
+      <c r="E7" t="inlineStr"/>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>150 kV</t>
+        </is>
+      </c>
+      <c r="G7" t="n">
         <v>1</v>
       </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>Beroperasi</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr"/>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Beroperasi</t>
+        </is>
+      </c>
       <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -6009,21 +6020,22 @@
           <t>ASAHI</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>150 kV</t>
-        </is>
-      </c>
-      <c r="F8" t="n">
+      <c r="E8" t="inlineStr"/>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>150 kV</t>
+        </is>
+      </c>
+      <c r="G8" t="n">
         <v>1</v>
       </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>Beroperasi</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr"/>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Beroperasi</t>
+        </is>
+      </c>
       <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -6044,21 +6056,22 @@
           <t>ASAHI</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>150 kV</t>
-        </is>
-      </c>
-      <c r="F9" t="n">
+      <c r="E9" t="inlineStr"/>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>150 kV</t>
+        </is>
+      </c>
+      <c r="G9" t="n">
         <v>1</v>
       </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>Beroperasi</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr"/>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Beroperasi</t>
+        </is>
+      </c>
       <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -6079,21 +6092,22 @@
           <t>CASRI</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>150 kV</t>
-        </is>
-      </c>
-      <c r="F10" t="n">
+      <c r="E10" t="inlineStr"/>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>150 kV</t>
+        </is>
+      </c>
+      <c r="G10" t="n">
         <v>1</v>
       </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>Beroperasi</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr"/>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Beroperasi</t>
+        </is>
+      </c>
       <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -6114,21 +6128,22 @@
           <t>CASRI</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>150 kV</t>
-        </is>
-      </c>
-      <c r="F11" t="n">
+      <c r="E11" t="inlineStr"/>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>150 kV</t>
+        </is>
+      </c>
+      <c r="G11" t="n">
         <v>1</v>
       </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>Beroperasi</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr"/>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Beroperasi</t>
+        </is>
+      </c>
       <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -6149,21 +6164,22 @@
           <t>CASRI</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>150 kV</t>
-        </is>
-      </c>
-      <c r="F12" t="n">
+      <c r="E12" t="inlineStr"/>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>150 kV</t>
+        </is>
+      </c>
+      <c r="G12" t="n">
         <v>1</v>
       </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>Beroperasi</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr"/>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Beroperasi</t>
+        </is>
+      </c>
       <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -6184,21 +6200,22 @@
           <t>GNMLA</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>150 kV</t>
-        </is>
-      </c>
-      <c r="F13" t="n">
+      <c r="E13" t="inlineStr"/>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>150 kV</t>
+        </is>
+      </c>
+      <c r="G13" t="n">
         <v>1</v>
       </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>Beroperasi</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr"/>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>Beroperasi</t>
+        </is>
+      </c>
       <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -6219,21 +6236,22 @@
           <t>CKNDE</t>
         </is>
       </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>150 kV</t>
-        </is>
-      </c>
-      <c r="F14" t="n">
+      <c r="E14" t="inlineStr"/>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>150 kV</t>
+        </is>
+      </c>
+      <c r="G14" t="n">
         <v>1</v>
       </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>Beroperasi</t>
-        </is>
-      </c>
-      <c r="H14" t="inlineStr"/>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>Beroperasi</t>
+        </is>
+      </c>
       <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -6254,21 +6272,22 @@
           <t>IKIAT</t>
         </is>
       </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>150 kV</t>
-        </is>
-      </c>
-      <c r="F15" t="n">
+      <c r="E15" t="inlineStr"/>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>150 kV</t>
+        </is>
+      </c>
+      <c r="G15" t="n">
         <v>1</v>
       </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>Beroperasi</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr"/>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>Beroperasi</t>
+        </is>
+      </c>
       <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -6289,21 +6308,22 @@
           <t>PUCAM</t>
         </is>
       </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>150 kV</t>
-        </is>
-      </c>
-      <c r="F16" t="n">
+      <c r="E16" t="inlineStr"/>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>150 kV</t>
+        </is>
+      </c>
+      <c r="G16" t="n">
         <v>1</v>
       </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>Beroperasi</t>
-        </is>
-      </c>
-      <c r="H16" t="inlineStr"/>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Beroperasi</t>
+        </is>
+      </c>
       <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -6324,21 +6344,22 @@
           <t>GORDA</t>
         </is>
       </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>150 kV</t>
-        </is>
-      </c>
-      <c r="F17" t="n">
+      <c r="E17" t="inlineStr"/>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>150 kV</t>
+        </is>
+      </c>
+      <c r="G17" t="n">
         <v>1</v>
       </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>Beroperasi</t>
-        </is>
-      </c>
-      <c r="H17" t="inlineStr"/>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>Beroperasi</t>
+        </is>
+      </c>
       <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -6359,21 +6380,22 @@
           <t>GORDA</t>
         </is>
       </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>150 kV</t>
-        </is>
-      </c>
-      <c r="F18" t="n">
+      <c r="E18" t="inlineStr"/>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>150 kV</t>
+        </is>
+      </c>
+      <c r="G18" t="n">
         <v>1</v>
       </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>Beroperasi</t>
-        </is>
-      </c>
-      <c r="H18" t="inlineStr"/>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>Beroperasi</t>
+        </is>
+      </c>
       <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -6394,21 +6416,22 @@
           <t>LBI</t>
         </is>
       </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>150 kV</t>
-        </is>
-      </c>
-      <c r="F19" t="n">
+      <c r="E19" t="inlineStr"/>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>150 kV</t>
+        </is>
+      </c>
+      <c r="G19" t="n">
         <v>1</v>
       </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>Beroperasi</t>
-        </is>
-      </c>
-      <c r="H19" t="inlineStr"/>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>Beroperasi</t>
+        </is>
+      </c>
       <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -6429,21 +6452,22 @@
           <t>BLRJA</t>
         </is>
       </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>150 kV</t>
-        </is>
-      </c>
-      <c r="F20" t="n">
+      <c r="E20" t="inlineStr"/>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>150 kV</t>
+        </is>
+      </c>
+      <c r="G20" t="n">
         <v>1</v>
       </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>Beroperasi</t>
-        </is>
-      </c>
-      <c r="H20" t="inlineStr"/>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>Beroperasi</t>
+        </is>
+      </c>
       <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/samples/ss_gucl_ingest.xlsx
+++ b/samples/ss_gucl_ingest.xlsx
@@ -495,7 +495,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U42"/>
+  <dimension ref="A1:U44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -664,7 +664,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>IBT 1,2,3 Cilegon Baru</t>
+          <t>IBT 1 Cilegon Baru</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -687,7 +687,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>1,2,3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="H3" t="inlineStr"/>
@@ -697,14 +697,10 @@
         </is>
       </c>
       <c r="J3" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>3 IBT (unit 1,2,3)</t>
-        </is>
-      </c>
+      <c r="L3" t="inlineStr"/>
       <c r="M3" t="inlineStr"/>
       <c r="N3" t="inlineStr">
         <is>
@@ -735,31 +731,41 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>PLTGU Cilegon</t>
+          <t>IBT 2 Cilegon Baru</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>KIT_PLTGU_CLG</t>
+          <t>IBT 2 CLBRU</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Pembangkit</t>
+          <t>IBT 3-Winding</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>150 kV</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr"/>
+          <t>500/150 kV</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="H4" t="inlineStr"/>
-      <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>CLBRU</t>
+        </is>
+      </c>
+      <c r="J4" t="n">
+        <v>1</v>
+      </c>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr"/>
@@ -771,10 +777,14 @@
       <c r="O4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Normal</t>
-        </is>
-      </c>
-      <c r="Q4" t="inlineStr"/>
+          <t>Rawan</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="R4" t="inlineStr">
         <is>
           <t>Banten</t>
@@ -788,31 +798,41 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>PLTU Labuan</t>
+          <t>IBT 3 Cilegon Baru</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>KIT_PLTU_LBN</t>
+          <t>IBT 3 CLBRU</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Pembangkit</t>
+          <t>IBT 3-Winding</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>150 kV</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr"/>
+          <t>500/150 kV</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="H5" t="inlineStr"/>
-      <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>CLBRU</t>
+        </is>
+      </c>
+      <c r="J5" t="n">
+        <v>1</v>
+      </c>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr"/>
@@ -824,10 +844,14 @@
       <c r="O5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Normal</t>
-        </is>
-      </c>
-      <c r="Q5" t="inlineStr"/>
+          <t>Rawan</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="R5" t="inlineStr">
         <is>
           <t>Banten</t>
@@ -841,12 +865,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>PLTU Asahi (aset milik)</t>
+          <t>PLTGU Cilegon</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>KIT_PLTU_ASAHI</t>
+          <t>KIT_PLTGU_CLG</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -855,7 +879,7 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -894,17 +918,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Cilegon Baru (bus 150 kV)</t>
+          <t>PLTU Labuan</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>CLBRU</t>
+          <t>KIT_PLTU_LBN</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Busbar GI</t>
+          <t>Pembangkit</t>
         </is>
       </c>
       <c r="E7" t="n">
@@ -930,14 +954,10 @@
       <c r="O7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Rawan</t>
-        </is>
-      </c>
-      <c r="Q7" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
         <is>
           <t>Banten</t>
@@ -951,21 +971,21 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Labuan</t>
+          <t>PLTU Asahi (aset milik)</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>LBUAN</t>
+          <t>KIT_PLTU_ASAHI</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Busbar GI</t>
+          <t>Pembangkit</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1004,12 +1024,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Kramatwatu</t>
+          <t>Cilegon Baru (bus 150 kV)</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>KRWTU</t>
+          <t>CLBRU</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1018,7 +1038,7 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1045,7 +1065,7 @@
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="R9" t="inlineStr">
@@ -1061,12 +1081,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>MNA / Trate</t>
+          <t>Labuan</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>MNA</t>
+          <t>LBUAN</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1075,7 +1095,7 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1097,14 +1117,10 @@
       <c r="O10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Rawan</t>
-        </is>
-      </c>
-      <c r="Q10" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
         <is>
           <t>Banten</t>
@@ -1118,12 +1134,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Alindo</t>
+          <t>Kramatwatu</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>ALNDO</t>
+          <t>KRWTU</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1154,10 +1170,14 @@
       <c r="O11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Normal</t>
-        </is>
-      </c>
-      <c r="Q11" t="inlineStr"/>
+          <t>Rawan</t>
+        </is>
+      </c>
+      <c r="Q11" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="R11" t="inlineStr">
         <is>
           <t>Banten</t>
@@ -1171,12 +1191,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>IFERO</t>
+          <t>MNA / Trate</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>INFRO</t>
+          <t>MNA</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1207,10 +1227,14 @@
       <c r="O12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Normal</t>
-        </is>
-      </c>
-      <c r="Q12" t="inlineStr"/>
+          <t>Rawan</t>
+        </is>
+      </c>
+      <c r="Q12" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="R12" t="inlineStr">
         <is>
           <t>Banten</t>
@@ -1224,12 +1248,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Asahimas</t>
+          <t>Alindo</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>ASAHI</t>
+          <t>ALNDO</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1260,14 +1284,10 @@
       <c r="O13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Rawan</t>
-        </is>
-      </c>
-      <c r="Q13" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr">
         <is>
           <t>Banten</t>
@@ -1281,12 +1301,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Krakatau Daya Listrik (KDL)</t>
+          <t>IFERO</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>KDL</t>
+          <t>INFRO</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -1334,12 +1354,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Cilegon Lama</t>
+          <t>Asahimas</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>CLGON</t>
+          <t>ASAHI</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -1370,10 +1390,14 @@
       <c r="O15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Normal</t>
-        </is>
-      </c>
-      <c r="Q15" t="inlineStr"/>
+          <t>Rawan</t>
+        </is>
+      </c>
+      <c r="Q15" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="R15" t="inlineStr">
         <is>
           <t>Banten</t>
@@ -1387,12 +1411,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Menes</t>
+          <t>Krakatau Daya Listrik (KDL)</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>MENES</t>
+          <t>KDL</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -1440,12 +1464,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Saketi</t>
+          <t>Cilegon Lama</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>SKETI</t>
+          <t>CLGON</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -1493,12 +1517,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Polyprima</t>
+          <t>Menes</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>POLMA</t>
+          <t>MENES</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -1529,14 +1553,10 @@
       <c r="O18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Rawan</t>
-        </is>
-      </c>
-      <c r="Q18" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="Q18" t="inlineStr"/>
       <c r="R18" t="inlineStr">
         <is>
           <t>Banten</t>
@@ -1550,12 +1570,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Serang</t>
+          <t>Saketi</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>SRANG</t>
+          <t>SKETI</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -1564,7 +1584,7 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -1586,14 +1606,10 @@
       <c r="O19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Rawan</t>
-        </is>
-      </c>
-      <c r="Q19" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="Q19" t="inlineStr"/>
       <c r="R19" t="inlineStr">
         <is>
           <t>Banten</t>
@@ -1607,12 +1623,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Cikande Serang (CASRI)</t>
+          <t>Polyprima</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>CASRI</t>
+          <t>POLMA</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -1621,7 +1637,7 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -1643,10 +1659,14 @@
       <c r="O20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Normal</t>
-        </is>
-      </c>
-      <c r="Q20" t="inlineStr"/>
+          <t>Rawan</t>
+        </is>
+      </c>
+      <c r="Q20" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
       <c r="R20" t="inlineStr">
         <is>
           <t>Banten</t>
@@ -1660,12 +1680,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Anyer</t>
+          <t>Serang</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>ANYER</t>
+          <t>SRANG</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -1696,10 +1716,14 @@
       <c r="O21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Normal</t>
-        </is>
-      </c>
-      <c r="Q21" t="inlineStr"/>
+          <t>Rawan</t>
+        </is>
+      </c>
+      <c r="Q21" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
       <c r="R21" t="inlineStr">
         <is>
           <t>Banten</t>
@@ -1713,12 +1737,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>KTT KSTEL</t>
+          <t>Cikande Serang (CASRI)</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>KSTEL</t>
+          <t>CASRI</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -1766,12 +1790,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Mitsui</t>
+          <t>Anyer</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>MITSUI</t>
+          <t>ANYER</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -1819,12 +1843,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>MCOIS</t>
+          <t>KTT KSTEL</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>MCOIS</t>
+          <t>KSTEL</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -1849,7 +1873,7 @@
       <c r="M24" t="inlineStr"/>
       <c r="N24" t="inlineStr">
         <is>
-          <t>Beroperasi</t>
+          <t>Milik Pelanggan</t>
         </is>
       </c>
       <c r="O24" t="inlineStr"/>
@@ -1872,12 +1896,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Rangkas Baru</t>
+          <t>Mitsui</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>RKBRU</t>
+          <t>MITSUI</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -1925,12 +1949,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Malimping</t>
+          <t>MCOIS</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>MPING</t>
+          <t>MCOIS</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -1978,12 +2002,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Gunung Malang (GMS)</t>
+          <t>Rangkas Baru</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>GNMLA</t>
+          <t>RKBRU</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -1992,7 +2016,7 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2014,14 +2038,10 @@
       <c r="O27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Rawan</t>
-        </is>
-      </c>
-      <c r="Q27" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="Q27" t="inlineStr"/>
       <c r="R27" t="inlineStr">
         <is>
           <t>Banten</t>
@@ -2035,12 +2055,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Baros</t>
+          <t>Malimping</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>BAROS</t>
+          <t>MPING</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -2049,7 +2069,7 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -2088,12 +2108,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Kopo Serang</t>
+          <t>Gunung Malang (GMS)</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>KOPOS</t>
+          <t>GNMLA</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -2129,7 +2149,7 @@
       </c>
       <c r="Q29" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="R29" t="inlineStr">
@@ -2145,12 +2165,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Bubulak Baru</t>
+          <t>Baros</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>BUBRU</t>
+          <t>BAROS</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -2198,12 +2218,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Bayah</t>
+          <t>Kopo Serang</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>BAYAH</t>
+          <t>KOPOS</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -2234,10 +2254,14 @@
       <c r="O31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Normal</t>
-        </is>
-      </c>
-      <c r="Q31" t="inlineStr"/>
+          <t>Rawan</t>
+        </is>
+      </c>
+      <c r="Q31" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="R31" t="inlineStr">
         <is>
           <t>Banten</t>
@@ -2251,12 +2275,12 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Indah Kiat</t>
+          <t>Bubulak Baru</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>IKIAT</t>
+          <t>BUBRU</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -2265,7 +2289,7 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -2287,14 +2311,10 @@
       <c r="O32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Rawan</t>
-        </is>
-      </c>
-      <c r="Q32" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="Q32" t="inlineStr"/>
       <c r="R32" t="inlineStr">
         <is>
           <t>Banten</t>
@@ -2308,21 +2328,21 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Cikande</t>
+          <t>Bayah</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>CKNDE</t>
+          <t>BAYAH</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Busbar GITET</t>
+          <t>Busbar GI</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -2344,14 +2364,10 @@
       <c r="O33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Rawan</t>
-        </is>
-      </c>
-      <c r="Q33" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="Q33" t="inlineStr"/>
       <c r="R33" t="inlineStr">
         <is>
           <t>Banten</t>
@@ -2365,12 +2381,12 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Rangkasbitung Kota</t>
+          <t>Indah Kiat</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>RGKOT</t>
+          <t>IKIAT</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -2401,10 +2417,14 @@
       <c r="O34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Normal</t>
-        </is>
-      </c>
-      <c r="Q34" t="inlineStr"/>
+          <t>Rawan</t>
+        </is>
+      </c>
+      <c r="Q34" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="R34" t="inlineStr">
         <is>
           <t>Banten</t>
@@ -2418,17 +2438,17 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Modern</t>
+          <t>Cikande</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>MDERN</t>
+          <t>CKNDE</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Busbar GI</t>
+          <t>Busbar GITET</t>
         </is>
       </c>
       <c r="E35" t="n">
@@ -2454,10 +2474,14 @@
       <c r="O35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Normal</t>
-        </is>
-      </c>
-      <c r="Q35" t="inlineStr"/>
+          <t>Rawan</t>
+        </is>
+      </c>
+      <c r="Q35" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="R35" t="inlineStr">
         <is>
           <t>Banten</t>
@@ -2471,12 +2495,12 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Labuan Industri</t>
+          <t>Rangkasbitung Kota</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>LBI</t>
+          <t>RGKOT</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -2524,12 +2548,12 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Balaraja (sisi Cilegon)</t>
+          <t>Modern</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>BLRJA</t>
+          <t>MDERN</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -2538,7 +2562,7 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -2560,14 +2584,10 @@
       <c r="O37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Rawan</t>
-        </is>
-      </c>
-      <c r="Q37" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="Q37" t="inlineStr"/>
       <c r="R37" t="inlineStr">
         <is>
           <t>Banten</t>
@@ -2581,12 +2601,12 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Pucam</t>
+          <t>Labuan Industri</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>PUCAM</t>
+          <t>LBI</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -2595,7 +2615,7 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -2617,14 +2637,10 @@
       <c r="O38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Rawan</t>
-        </is>
-      </c>
-      <c r="Q38" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="Q38" t="inlineStr"/>
       <c r="R38" t="inlineStr">
         <is>
           <t>Banten</t>
@@ -2638,12 +2654,12 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Kopo</t>
+          <t>Balaraja (sisi Cilegon)</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>KOPO</t>
+          <t>BLRJA</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -2674,10 +2690,14 @@
       <c r="O39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Normal</t>
-        </is>
-      </c>
-      <c r="Q39" t="inlineStr"/>
+          <t>Rawan</t>
+        </is>
+      </c>
+      <c r="Q39" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="R39" t="inlineStr">
         <is>
           <t>Banten</t>
@@ -2691,12 +2711,12 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Gorda</t>
+          <t>Pucam</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>GORDA</t>
+          <t>PUCAM</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -2705,7 +2725,7 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -2732,7 +2752,7 @@
       </c>
       <c r="Q40" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>2</t>
         </is>
       </c>
       <c r="R40" t="inlineStr">
@@ -2748,12 +2768,12 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>New Balaraja</t>
+          <t>Kopo</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>NBRJA</t>
+          <t>KOPO</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -2762,7 +2782,7 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -2801,12 +2821,12 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Suvarna</t>
+          <t>Gorda</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>SVRNA</t>
+          <t>GORDA</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -2837,16 +2857,126 @@
       <c r="O42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
+          <t>Rawan</t>
+        </is>
+      </c>
+      <c r="Q42" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="R42" t="inlineStr">
+        <is>
+          <t>Banten</t>
+        </is>
+      </c>
+      <c r="S42" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>42</v>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>New Balaraja</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>NBRJA</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>Busbar GI</t>
+        </is>
+      </c>
+      <c r="E43" t="n">
+        <v>6</v>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>150 kV</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr"/>
+      <c r="H43" t="inlineStr"/>
+      <c r="I43" t="inlineStr"/>
+      <c r="J43" t="inlineStr"/>
+      <c r="K43" t="inlineStr"/>
+      <c r="L43" t="inlineStr"/>
+      <c r="M43" t="inlineStr"/>
+      <c r="N43" t="inlineStr">
+        <is>
+          <t>Beroperasi</t>
+        </is>
+      </c>
+      <c r="O43" t="inlineStr"/>
+      <c r="P43" t="inlineStr">
+        <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="Q42" t="inlineStr"/>
-      <c r="R42" t="inlineStr">
-        <is>
-          <t>Banten</t>
-        </is>
-      </c>
-      <c r="S42" t="inlineStr"/>
+      <c r="Q43" t="inlineStr"/>
+      <c r="R43" t="inlineStr">
+        <is>
+          <t>Banten</t>
+        </is>
+      </c>
+      <c r="S43" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>43</v>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>Suvarna</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>SVRNA</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>Busbar GI</t>
+        </is>
+      </c>
+      <c r="E44" t="n">
+        <v>6</v>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>150 kV</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr"/>
+      <c r="H44" t="inlineStr"/>
+      <c r="I44" t="inlineStr"/>
+      <c r="J44" t="inlineStr"/>
+      <c r="K44" t="inlineStr"/>
+      <c r="L44" t="inlineStr"/>
+      <c r="M44" t="inlineStr"/>
+      <c r="N44" t="inlineStr">
+        <is>
+          <t>Beroperasi</t>
+        </is>
+      </c>
+      <c r="O44" t="inlineStr"/>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="Q44" t="inlineStr"/>
+      <c r="R44" t="inlineStr">
+        <is>
+          <t>Banten</t>
+        </is>
+      </c>
+      <c r="S44" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
